--- a/main/ig/StructureDefinition-sas-sos-appointment.xlsx
+++ b/main/ig/StructureDefinition-sas-sos-appointment.xlsx
@@ -54,7 +54,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-07-03T13:50:07+00:00</t>
+    <t>2024-07-03T13:52:48+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-sas-sos-appointment.xlsx
+++ b/main/ig/StructureDefinition-sas-sos-appointment.xlsx
@@ -54,7 +54,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-07-03T13:52:48+00:00</t>
+    <t>2024-07-03T13:54:46+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-sas-sos-appointment.xlsx
+++ b/main/ig/StructureDefinition-sas-sos-appointment.xlsx
@@ -54,7 +54,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-07-03T13:54:46+00:00</t>
+    <t>2024-07-04T13:52:01+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-sas-sos-appointment.xlsx
+++ b/main/ig/StructureDefinition-sas-sos-appointment.xlsx
@@ -54,7 +54,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-07-04T13:52:01+00:00</t>
+    <t>2024-07-09T12:16:32+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-sas-sos-appointment.xlsx
+++ b/main/ig/StructureDefinition-sas-sos-appointment.xlsx
@@ -54,7 +54,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-07-09T12:16:32+00:00</t>
+    <t>2024-07-09T12:36:00+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-sas-sos-appointment.xlsx
+++ b/main/ig/StructureDefinition-sas-sos-appointment.xlsx
@@ -54,7 +54,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-07-09T12:36:00+00:00</t>
+    <t>2024-07-12T14:55:46+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-sas-sos-appointment.xlsx
+++ b/main/ig/StructureDefinition-sas-sos-appointment.xlsx
@@ -54,7 +54,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-07-12T14:55:46+00:00</t>
+    <t>2024-07-17T06:26:56+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-sas-sos-appointment.xlsx
+++ b/main/ig/StructureDefinition-sas-sos-appointment.xlsx
@@ -54,7 +54,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-07-17T06:26:56+00:00</t>
+    <t>2024-07-17T06:40:14+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-sas-sos-appointment.xlsx
+++ b/main/ig/StructureDefinition-sas-sos-appointment.xlsx
@@ -54,7 +54,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-07-17T06:40:14+00:00</t>
+    <t>2024-07-17T06:51:58+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-sas-sos-appointment.xlsx
+++ b/main/ig/StructureDefinition-sas-sos-appointment.xlsx
@@ -54,7 +54,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-07-17T06:51:58+00:00</t>
+    <t>2024-07-17T17:08:26+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-sas-sos-appointment.xlsx
+++ b/main/ig/StructureDefinition-sas-sos-appointment.xlsx
@@ -54,7 +54,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-07-17T17:08:26+00:00</t>
+    <t>2024-07-17T17:33:21+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-sas-sos-appointment.xlsx
+++ b/main/ig/StructureDefinition-sas-sos-appointment.xlsx
@@ -54,7 +54,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-07-17T17:33:21+00:00</t>
+    <t>2024-07-18T16:11:48+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-sas-sos-appointment.xlsx
+++ b/main/ig/StructureDefinition-sas-sos-appointment.xlsx
@@ -54,7 +54,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-07-18T16:11:48+00:00</t>
+    <t>2024-07-19T13:28:45+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-sas-sos-appointment.xlsx
+++ b/main/ig/StructureDefinition-sas-sos-appointment.xlsx
@@ -54,7 +54,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-07-19T13:28:45+00:00</t>
+    <t>2024-07-19T14:51:36+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-sas-sos-appointment.xlsx
+++ b/main/ig/StructureDefinition-sas-sos-appointment.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-11-25T08:03:17+00:00</t>
+    <t>2025-12-11T11:06:01+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-sas-sos-appointment.xlsx
+++ b/main/ig/StructureDefinition-sas-sos-appointment.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-12-11T11:06:01+00:00</t>
+    <t>2026-05-06T06:43:41+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-sas-sos-appointment.xlsx
+++ b/main/ig/StructureDefinition-sas-sos-appointment.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-05-06T06:43:41+00:00</t>
+    <t>2026-05-07T11:54:31+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -75,7 +75,7 @@
     <t>Jurisdiction</t>
   </si>
   <si>
-    <t>FRANCE</t>
+    <t>France (la)</t>
   </si>
   <si>
     <t>Description</t>

--- a/main/ig/StructureDefinition-sas-sos-appointment.xlsx
+++ b/main/ig/StructureDefinition-sas-sos-appointment.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-15T12:59:24+00:00</t>
+    <t>2026-06-15T13:14:04+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -1412,7 +1412,7 @@
     <t>Participation status of the actor.</t>
   </si>
   <si>
-    <t>https://interop.esante.gouv.fr/ig/fhir/sas/ValueSet/sas-sos-valueset-participant-status</t>
+    <t>https://interop.esante.gouv.fr/ig/fhir/sas/ValueSet/sas-valueset-participant-status</t>
   </si>
   <si>
     <t>Appointment.participant.period</t>
@@ -1777,7 +1777,7 @@
     <col min="23" max="23" width="16.3203125" customWidth="true" bestFit="true"/>
     <col min="24" max="24" width="16.16796875" customWidth="true" bestFit="true"/>
     <col min="25" max="25" width="84.33984375" customWidth="true" bestFit="true"/>
-    <col min="26" max="26" width="67.92578125" customWidth="true" bestFit="true"/>
+    <col min="26" max="26" width="64.7578125" customWidth="true" bestFit="true"/>
     <col min="27" max="27" width="5.44140625" customWidth="true" bestFit="true"/>
     <col min="28" max="28" width="19.4765625" customWidth="true" bestFit="true"/>
     <col min="29" max="29" width="36.0390625" customWidth="true" bestFit="true"/>

--- a/main/ig/StructureDefinition-sas-sos-appointment.xlsx
+++ b/main/ig/StructureDefinition-sas-sos-appointment.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-15T13:14:04+00:00</t>
+    <t>2026-06-17T07:51:28+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-sas-sos-appointment.xlsx
+++ b/main/ig/StructureDefinition-sas-sos-appointment.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-17T07:51:28+00:00</t>
+    <t>2026-06-22T16:38:09+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-sas-sos-appointment.xlsx
+++ b/main/ig/StructureDefinition-sas-sos-appointment.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-22T16:38:09+00:00</t>
+    <t>2026-06-26T14:40:16+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-sas-sos-appointment.xlsx
+++ b/main/ig/StructureDefinition-sas-sos-appointment.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-26T14:40:16+00:00</t>
+    <t>2026-06-29T13:29:33+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-sas-sos-appointment.xlsx
+++ b/main/ig/StructureDefinition-sas-sos-appointment.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-29T13:29:33+00:00</t>
+    <t>2026-07-06T10:07:23+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-sas-sos-appointment.xlsx
+++ b/main/ig/StructureDefinition-sas-sos-appointment.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-06T10:07:23+00:00</t>
+    <t>2026-07-06T12:34:55+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-sas-sos-appointment.xlsx
+++ b/main/ig/StructureDefinition-sas-sos-appointment.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-06T12:34:55+00:00</t>
+    <t>2026-07-06T15:16:18+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-sas-sos-appointment.xlsx
+++ b/main/ig/StructureDefinition-sas-sos-appointment.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-06T15:16:18+00:00</t>
+    <t>2026-07-09T08:50:24+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-sas-sos-appointment.xlsx
+++ b/main/ig/StructureDefinition-sas-sos-appointment.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-09T08:50:24+00:00</t>
+    <t>2026-07-10T14:30:27+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-sas-sos-appointment.xlsx
+++ b/main/ig/StructureDefinition-sas-sos-appointment.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-10T14:30:27+00:00</t>
+    <t>2026-07-15T07:07:52+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-sas-sos-appointment.xlsx
+++ b/main/ig/StructureDefinition-sas-sos-appointment.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-15T07:07:52+00:00</t>
+    <t>2026-07-15T08:40:44+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-sas-sos-appointment.xlsx
+++ b/main/ig/StructureDefinition-sas-sos-appointment.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-15T08:40:44+00:00</t>
+    <t>2026-07-17T08:17:39+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-sas-sos-appointment.xlsx
+++ b/main/ig/StructureDefinition-sas-sos-appointment.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-17T08:17:39+00:00</t>
+    <t>2026-07-20T10:02:38+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-sas-sos-appointment.xlsx
+++ b/main/ig/StructureDefinition-sas-sos-appointment.xlsx
@@ -16,7 +16,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2560" uniqueCount="453">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2559" uniqueCount="452">
   <si>
     <t>Property</t>
   </si>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-20T10:02:38+00:00</t>
+    <t>2026-08-18T14:54:32+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -1057,10 +1057,7 @@
 This element is labeled as a modifier because the status contains the code entered-in-error that mark the Appointment as not currently valid.</t>
   </si>
   <si>
-    <t>The free/busy status of an appointment.</t>
-  </si>
-  <si>
-    <t>http://hl7.org/fhir/ValueSet/appointmentstatus</t>
+    <t>https://interop.esante.gouv.fr/ig/fhir/sas/ValueSet/sas-valueset-appointment-status</t>
   </si>
   <si>
     <t>Appointment.cancelationReason</t>
@@ -1777,7 +1774,7 @@
     <col min="23" max="23" width="16.3203125" customWidth="true" bestFit="true"/>
     <col min="24" max="24" width="16.16796875" customWidth="true" bestFit="true"/>
     <col min="25" max="25" width="84.33984375" customWidth="true" bestFit="true"/>
-    <col min="26" max="26" width="64.7578125" customWidth="true" bestFit="true"/>
+    <col min="26" max="26" width="66.3046875" customWidth="true" bestFit="true"/>
     <col min="27" max="27" width="5.44140625" customWidth="true" bestFit="true"/>
     <col min="28" max="28" width="19.4765625" customWidth="true" bestFit="true"/>
     <col min="29" max="29" width="36.0390625" customWidth="true" bestFit="true"/>
@@ -6960,11 +6957,9 @@
       <c r="X51" t="s" s="2">
         <v>205</v>
       </c>
-      <c r="Y51" t="s" s="2">
+      <c r="Y51" s="2"/>
+      <c r="Z51" t="s" s="2">
         <v>334</v>
-      </c>
-      <c r="Z51" t="s" s="2">
-        <v>335</v>
       </c>
       <c r="AA51" t="s" s="2">
         <v>72</v>
@@ -6999,10 +6994,10 @@
     </row>
     <row r="52" hidden="true">
       <c r="A52" t="s" s="2">
-        <v>336</v>
+        <v>335</v>
       </c>
       <c r="B52" t="s" s="2">
-        <v>336</v>
+        <v>335</v>
       </c>
       <c r="C52" s="2"/>
       <c r="D52" t="s" s="2">
@@ -7028,13 +7023,13 @@
         <v>211</v>
       </c>
       <c r="L52" t="s" s="2">
+        <v>336</v>
+      </c>
+      <c r="M52" t="s" s="2">
         <v>337</v>
       </c>
-      <c r="M52" t="s" s="2">
+      <c r="N52" t="s" s="2">
         <v>338</v>
-      </c>
-      <c r="N52" t="s" s="2">
-        <v>339</v>
       </c>
       <c r="O52" s="2"/>
       <c r="P52" t="s" s="2">
@@ -7060,11 +7055,11 @@
         <v>72</v>
       </c>
       <c r="X52" t="s" s="2">
-        <v>340</v>
+        <v>339</v>
       </c>
       <c r="Y52" s="2"/>
       <c r="Z52" t="s" s="2">
-        <v>341</v>
+        <v>340</v>
       </c>
       <c r="AA52" t="s" s="2">
         <v>72</v>
@@ -7082,7 +7077,7 @@
         <v>72</v>
       </c>
       <c r="AF52" t="s" s="2">
-        <v>336</v>
+        <v>335</v>
       </c>
       <c r="AG52" t="s" s="2">
         <v>73</v>
@@ -7099,10 +7094,10 @@
     </row>
     <row r="53" hidden="true">
       <c r="A53" t="s" s="2">
-        <v>342</v>
+        <v>341</v>
       </c>
       <c r="B53" t="s" s="2">
-        <v>342</v>
+        <v>341</v>
       </c>
       <c r="C53" s="2"/>
       <c r="D53" t="s" s="2">
@@ -7128,13 +7123,13 @@
         <v>211</v>
       </c>
       <c r="L53" t="s" s="2">
+        <v>342</v>
+      </c>
+      <c r="M53" t="s" s="2">
         <v>343</v>
       </c>
-      <c r="M53" t="s" s="2">
-        <v>344</v>
-      </c>
       <c r="N53" t="s" s="2">
-        <v>339</v>
+        <v>338</v>
       </c>
       <c r="O53" s="2"/>
       <c r="P53" t="s" s="2">
@@ -7160,11 +7155,11 @@
         <v>72</v>
       </c>
       <c r="X53" t="s" s="2">
-        <v>340</v>
+        <v>339</v>
       </c>
       <c r="Y53" s="2"/>
       <c r="Z53" t="s" s="2">
-        <v>345</v>
+        <v>344</v>
       </c>
       <c r="AA53" t="s" s="2">
         <v>72</v>
@@ -7182,7 +7177,7 @@
         <v>72</v>
       </c>
       <c r="AF53" t="s" s="2">
-        <v>342</v>
+        <v>341</v>
       </c>
       <c r="AG53" t="s" s="2">
         <v>73</v>
@@ -7199,10 +7194,10 @@
     </row>
     <row r="54" hidden="true">
       <c r="A54" t="s" s="2">
-        <v>346</v>
+        <v>345</v>
       </c>
       <c r="B54" t="s" s="2">
-        <v>346</v>
+        <v>345</v>
       </c>
       <c r="C54" s="2"/>
       <c r="D54" t="s" s="2">
@@ -7228,13 +7223,13 @@
         <v>211</v>
       </c>
       <c r="L54" t="s" s="2">
+        <v>346</v>
+      </c>
+      <c r="M54" t="s" s="2">
         <v>347</v>
       </c>
-      <c r="M54" t="s" s="2">
+      <c r="N54" t="s" s="2">
         <v>348</v>
-      </c>
-      <c r="N54" t="s" s="2">
-        <v>349</v>
       </c>
       <c r="O54" s="2"/>
       <c r="P54" t="s" s="2">
@@ -7260,11 +7255,11 @@
         <v>72</v>
       </c>
       <c r="X54" t="s" s="2">
-        <v>340</v>
+        <v>339</v>
       </c>
       <c r="Y54" s="2"/>
       <c r="Z54" t="s" s="2">
-        <v>350</v>
+        <v>349</v>
       </c>
       <c r="AA54" t="s" s="2">
         <v>72</v>
@@ -7282,7 +7277,7 @@
         <v>72</v>
       </c>
       <c r="AF54" t="s" s="2">
-        <v>346</v>
+        <v>345</v>
       </c>
       <c r="AG54" t="s" s="2">
         <v>73</v>
@@ -7299,10 +7294,10 @@
     </row>
     <row r="55" hidden="true">
       <c r="A55" t="s" s="2">
-        <v>351</v>
+        <v>350</v>
       </c>
       <c r="B55" t="s" s="2">
-        <v>351</v>
+        <v>350</v>
       </c>
       <c r="C55" s="2"/>
       <c r="D55" t="s" s="2">
@@ -7328,13 +7323,13 @@
         <v>211</v>
       </c>
       <c r="L55" t="s" s="2">
+        <v>351</v>
+      </c>
+      <c r="M55" t="s" s="2">
         <v>352</v>
       </c>
-      <c r="M55" t="s" s="2">
-        <v>353</v>
-      </c>
       <c r="N55" t="s" s="2">
-        <v>339</v>
+        <v>338</v>
       </c>
       <c r="O55" s="2"/>
       <c r="P55" t="s" s="2">
@@ -7364,7 +7359,7 @@
       </c>
       <c r="Y55" s="2"/>
       <c r="Z55" t="s" s="2">
-        <v>354</v>
+        <v>353</v>
       </c>
       <c r="AA55" t="s" s="2">
         <v>72</v>
@@ -7382,7 +7377,7 @@
         <v>72</v>
       </c>
       <c r="AF55" t="s" s="2">
-        <v>351</v>
+        <v>350</v>
       </c>
       <c r="AG55" t="s" s="2">
         <v>73</v>
@@ -7399,10 +7394,10 @@
     </row>
     <row r="56" hidden="true">
       <c r="A56" t="s" s="2">
-        <v>355</v>
+        <v>354</v>
       </c>
       <c r="B56" t="s" s="2">
-        <v>355</v>
+        <v>354</v>
       </c>
       <c r="C56" s="2"/>
       <c r="D56" t="s" s="2">
@@ -7428,13 +7423,13 @@
         <v>211</v>
       </c>
       <c r="L56" t="s" s="2">
+        <v>355</v>
+      </c>
+      <c r="M56" t="s" s="2">
         <v>356</v>
       </c>
-      <c r="M56" t="s" s="2">
-        <v>357</v>
-      </c>
       <c r="N56" t="s" s="2">
-        <v>339</v>
+        <v>338</v>
       </c>
       <c r="O56" s="2"/>
       <c r="P56" t="s" s="2">
@@ -7464,7 +7459,7 @@
       </c>
       <c r="Y56" s="2"/>
       <c r="Z56" t="s" s="2">
-        <v>358</v>
+        <v>357</v>
       </c>
       <c r="AA56" t="s" s="2">
         <v>72</v>
@@ -7482,7 +7477,7 @@
         <v>72</v>
       </c>
       <c r="AF56" t="s" s="2">
-        <v>355</v>
+        <v>354</v>
       </c>
       <c r="AG56" t="s" s="2">
         <v>73</v>
@@ -7499,10 +7494,10 @@
     </row>
     <row r="57" hidden="true">
       <c r="A57" t="s" s="2">
-        <v>359</v>
+        <v>358</v>
       </c>
       <c r="B57" t="s" s="2">
-        <v>359</v>
+        <v>358</v>
       </c>
       <c r="C57" s="2"/>
       <c r="D57" t="s" s="2">
@@ -7528,13 +7523,13 @@
         <v>211</v>
       </c>
       <c r="L57" t="s" s="2">
+        <v>359</v>
+      </c>
+      <c r="M57" t="s" s="2">
         <v>360</v>
       </c>
-      <c r="M57" t="s" s="2">
-        <v>361</v>
-      </c>
       <c r="N57" t="s" s="2">
-        <v>339</v>
+        <v>338</v>
       </c>
       <c r="O57" s="2"/>
       <c r="P57" t="s" s="2">
@@ -7563,11 +7558,11 @@
         <v>105</v>
       </c>
       <c r="Y57" t="s" s="2">
+        <v>361</v>
+      </c>
+      <c r="Z57" t="s" s="2">
         <v>362</v>
       </c>
-      <c r="Z57" t="s" s="2">
-        <v>363</v>
-      </c>
       <c r="AA57" t="s" s="2">
         <v>72</v>
       </c>
@@ -7584,7 +7579,7 @@
         <v>72</v>
       </c>
       <c r="AF57" t="s" s="2">
-        <v>359</v>
+        <v>358</v>
       </c>
       <c r="AG57" t="s" s="2">
         <v>73</v>
@@ -7601,10 +7596,10 @@
     </row>
     <row r="58" hidden="true">
       <c r="A58" t="s" s="2">
-        <v>364</v>
+        <v>363</v>
       </c>
       <c r="B58" t="s" s="2">
-        <v>364</v>
+        <v>363</v>
       </c>
       <c r="C58" s="2"/>
       <c r="D58" t="s" s="2">
@@ -7627,16 +7622,16 @@
         <v>72</v>
       </c>
       <c r="K58" t="s" s="2">
+        <v>364</v>
+      </c>
+      <c r="L58" t="s" s="2">
         <v>365</v>
       </c>
-      <c r="L58" t="s" s="2">
+      <c r="M58" t="s" s="2">
         <v>366</v>
       </c>
-      <c r="M58" t="s" s="2">
+      <c r="N58" t="s" s="2">
         <v>367</v>
-      </c>
-      <c r="N58" t="s" s="2">
-        <v>368</v>
       </c>
       <c r="O58" s="2"/>
       <c r="P58" t="s" s="2">
@@ -7686,7 +7681,7 @@
         <v>72</v>
       </c>
       <c r="AF58" t="s" s="2">
-        <v>364</v>
+        <v>363</v>
       </c>
       <c r="AG58" t="s" s="2">
         <v>73</v>
@@ -7703,10 +7698,10 @@
     </row>
     <row r="59" hidden="true">
       <c r="A59" t="s" s="2">
-        <v>369</v>
+        <v>368</v>
       </c>
       <c r="B59" t="s" s="2">
-        <v>369</v>
+        <v>368</v>
       </c>
       <c r="C59" s="2"/>
       <c r="D59" t="s" s="2">
@@ -7729,16 +7724,16 @@
         <v>72</v>
       </c>
       <c r="K59" t="s" s="2">
+        <v>369</v>
+      </c>
+      <c r="L59" t="s" s="2">
         <v>370</v>
       </c>
-      <c r="L59" t="s" s="2">
+      <c r="M59" t="s" s="2">
         <v>371</v>
       </c>
-      <c r="M59" t="s" s="2">
+      <c r="N59" t="s" s="2">
         <v>372</v>
-      </c>
-      <c r="N59" t="s" s="2">
-        <v>373</v>
       </c>
       <c r="O59" s="2"/>
       <c r="P59" t="s" s="2">
@@ -7788,7 +7783,7 @@
         <v>72</v>
       </c>
       <c r="AF59" t="s" s="2">
-        <v>369</v>
+        <v>368</v>
       </c>
       <c r="AG59" t="s" s="2">
         <v>73</v>
@@ -7805,10 +7800,10 @@
     </row>
     <row r="60" hidden="true">
       <c r="A60" t="s" s="2">
-        <v>374</v>
+        <v>373</v>
       </c>
       <c r="B60" t="s" s="2">
-        <v>374</v>
+        <v>373</v>
       </c>
       <c r="C60" s="2"/>
       <c r="D60" t="s" s="2">
@@ -7834,10 +7829,10 @@
         <v>139</v>
       </c>
       <c r="L60" t="s" s="2">
+        <v>374</v>
+      </c>
+      <c r="M60" t="s" s="2">
         <v>375</v>
-      </c>
-      <c r="M60" t="s" s="2">
-        <v>376</v>
       </c>
       <c r="N60" t="s" s="2">
         <v>253</v>
@@ -7890,7 +7885,7 @@
         <v>72</v>
       </c>
       <c r="AF60" t="s" s="2">
-        <v>374</v>
+        <v>373</v>
       </c>
       <c r="AG60" t="s" s="2">
         <v>73</v>
@@ -7907,10 +7902,10 @@
     </row>
     <row r="61" hidden="true">
       <c r="A61" t="s" s="2">
-        <v>377</v>
+        <v>376</v>
       </c>
       <c r="B61" t="s" s="2">
-        <v>377</v>
+        <v>376</v>
       </c>
       <c r="C61" s="2"/>
       <c r="D61" t="s" s="2">
@@ -7933,16 +7928,16 @@
         <v>72</v>
       </c>
       <c r="K61" t="s" s="2">
+        <v>377</v>
+      </c>
+      <c r="L61" t="s" s="2">
         <v>378</v>
       </c>
-      <c r="L61" t="s" s="2">
+      <c r="M61" t="s" s="2">
         <v>379</v>
       </c>
-      <c r="M61" t="s" s="2">
-        <v>380</v>
-      </c>
       <c r="N61" t="s" s="2">
-        <v>368</v>
+        <v>367</v>
       </c>
       <c r="O61" s="2"/>
       <c r="P61" t="s" s="2">
@@ -7992,7 +7987,7 @@
         <v>72</v>
       </c>
       <c r="AF61" t="s" s="2">
-        <v>377</v>
+        <v>376</v>
       </c>
       <c r="AG61" t="s" s="2">
         <v>73</v>
@@ -8009,10 +8004,10 @@
     </row>
     <row r="62" hidden="true">
       <c r="A62" t="s" s="2">
-        <v>381</v>
+        <v>380</v>
       </c>
       <c r="B62" t="s" s="2">
-        <v>381</v>
+        <v>380</v>
       </c>
       <c r="C62" s="2"/>
       <c r="D62" t="s" s="2">
@@ -8035,16 +8030,16 @@
         <v>81</v>
       </c>
       <c r="K62" t="s" s="2">
+        <v>381</v>
+      </c>
+      <c r="L62" t="s" s="2">
         <v>382</v>
       </c>
-      <c r="L62" t="s" s="2">
+      <c r="M62" t="s" s="2">
         <v>383</v>
       </c>
-      <c r="M62" t="s" s="2">
+      <c r="N62" t="s" s="2">
         <v>384</v>
-      </c>
-      <c r="N62" t="s" s="2">
-        <v>385</v>
       </c>
       <c r="O62" s="2"/>
       <c r="P62" t="s" s="2">
@@ -8094,7 +8089,7 @@
         <v>72</v>
       </c>
       <c r="AF62" t="s" s="2">
-        <v>381</v>
+        <v>380</v>
       </c>
       <c r="AG62" t="s" s="2">
         <v>73</v>
@@ -8111,10 +8106,10 @@
     </row>
     <row r="63" hidden="true">
       <c r="A63" t="s" s="2">
-        <v>386</v>
+        <v>385</v>
       </c>
       <c r="B63" t="s" s="2">
-        <v>386</v>
+        <v>385</v>
       </c>
       <c r="C63" s="2"/>
       <c r="D63" t="s" s="2">
@@ -8137,16 +8132,16 @@
         <v>81</v>
       </c>
       <c r="K63" t="s" s="2">
-        <v>382</v>
+        <v>381</v>
       </c>
       <c r="L63" t="s" s="2">
+        <v>386</v>
+      </c>
+      <c r="M63" t="s" s="2">
         <v>387</v>
       </c>
-      <c r="M63" t="s" s="2">
-        <v>388</v>
-      </c>
       <c r="N63" t="s" s="2">
-        <v>385</v>
+        <v>384</v>
       </c>
       <c r="O63" s="2"/>
       <c r="P63" t="s" s="2">
@@ -8196,7 +8191,7 @@
         <v>72</v>
       </c>
       <c r="AF63" t="s" s="2">
-        <v>386</v>
+        <v>385</v>
       </c>
       <c r="AG63" t="s" s="2">
         <v>73</v>
@@ -8213,10 +8208,10 @@
     </row>
     <row r="64" hidden="true">
       <c r="A64" t="s" s="2">
-        <v>389</v>
+        <v>388</v>
       </c>
       <c r="B64" t="s" s="2">
-        <v>389</v>
+        <v>388</v>
       </c>
       <c r="C64" s="2"/>
       <c r="D64" t="s" s="2">
@@ -8239,16 +8234,16 @@
         <v>72</v>
       </c>
       <c r="K64" t="s" s="2">
+        <v>389</v>
+      </c>
+      <c r="L64" t="s" s="2">
         <v>390</v>
       </c>
-      <c r="L64" t="s" s="2">
+      <c r="M64" t="s" s="2">
         <v>391</v>
       </c>
-      <c r="M64" t="s" s="2">
+      <c r="N64" t="s" s="2">
         <v>392</v>
-      </c>
-      <c r="N64" t="s" s="2">
-        <v>393</v>
       </c>
       <c r="O64" s="2"/>
       <c r="P64" t="s" s="2">
@@ -8298,7 +8293,7 @@
         <v>72</v>
       </c>
       <c r="AF64" t="s" s="2">
-        <v>389</v>
+        <v>388</v>
       </c>
       <c r="AG64" t="s" s="2">
         <v>73</v>
@@ -8315,10 +8310,10 @@
     </row>
     <row r="65" hidden="true">
       <c r="A65" t="s" s="2">
-        <v>394</v>
+        <v>393</v>
       </c>
       <c r="B65" t="s" s="2">
-        <v>394</v>
+        <v>393</v>
       </c>
       <c r="C65" s="2"/>
       <c r="D65" t="s" s="2">
@@ -8341,16 +8336,16 @@
         <v>72</v>
       </c>
       <c r="K65" t="s" s="2">
+        <v>394</v>
+      </c>
+      <c r="L65" t="s" s="2">
         <v>395</v>
       </c>
-      <c r="L65" t="s" s="2">
+      <c r="M65" t="s" s="2">
         <v>396</v>
       </c>
-      <c r="M65" t="s" s="2">
-        <v>397</v>
-      </c>
       <c r="N65" t="s" s="2">
-        <v>368</v>
+        <v>367</v>
       </c>
       <c r="O65" s="2"/>
       <c r="P65" t="s" s="2">
@@ -8400,7 +8395,7 @@
         <v>72</v>
       </c>
       <c r="AF65" t="s" s="2">
-        <v>394</v>
+        <v>393</v>
       </c>
       <c r="AG65" t="s" s="2">
         <v>73</v>
@@ -8417,10 +8412,10 @@
     </row>
     <row r="66">
       <c r="A66" t="s" s="2">
-        <v>398</v>
+        <v>397</v>
       </c>
       <c r="B66" t="s" s="2">
-        <v>398</v>
+        <v>397</v>
       </c>
       <c r="C66" s="2"/>
       <c r="D66" t="s" s="2">
@@ -8443,16 +8438,16 @@
         <v>72</v>
       </c>
       <c r="K66" t="s" s="2">
+        <v>398</v>
+      </c>
+      <c r="L66" t="s" s="2">
         <v>399</v>
       </c>
-      <c r="L66" t="s" s="2">
+      <c r="M66" t="s" s="2">
         <v>400</v>
       </c>
-      <c r="M66" t="s" s="2">
+      <c r="N66" t="s" s="2">
         <v>401</v>
-      </c>
-      <c r="N66" t="s" s="2">
-        <v>402</v>
       </c>
       <c r="O66" s="2"/>
       <c r="P66" t="s" s="2">
@@ -8502,7 +8497,7 @@
         <v>72</v>
       </c>
       <c r="AF66" t="s" s="2">
-        <v>398</v>
+        <v>397</v>
       </c>
       <c r="AG66" t="s" s="2">
         <v>73</v>
@@ -8519,10 +8514,10 @@
     </row>
     <row r="67" hidden="true">
       <c r="A67" t="s" s="2">
-        <v>403</v>
+        <v>402</v>
       </c>
       <c r="B67" t="s" s="2">
-        <v>403</v>
+        <v>402</v>
       </c>
       <c r="C67" s="2"/>
       <c r="D67" t="s" s="2">
@@ -8548,13 +8543,13 @@
         <v>139</v>
       </c>
       <c r="L67" t="s" s="2">
+        <v>403</v>
+      </c>
+      <c r="M67" t="s" s="2">
         <v>404</v>
       </c>
-      <c r="M67" t="s" s="2">
+      <c r="N67" t="s" s="2">
         <v>405</v>
-      </c>
-      <c r="N67" t="s" s="2">
-        <v>406</v>
       </c>
       <c r="O67" s="2"/>
       <c r="P67" t="s" s="2">
@@ -8604,7 +8599,7 @@
         <v>72</v>
       </c>
       <c r="AF67" t="s" s="2">
-        <v>403</v>
+        <v>402</v>
       </c>
       <c r="AG67" t="s" s="2">
         <v>73</v>
@@ -8621,10 +8616,10 @@
     </row>
     <row r="68" hidden="true">
       <c r="A68" t="s" s="2">
-        <v>407</v>
+        <v>406</v>
       </c>
       <c r="B68" t="s" s="2">
-        <v>407</v>
+        <v>406</v>
       </c>
       <c r="C68" s="2"/>
       <c r="D68" t="s" s="2">
@@ -8650,10 +8645,10 @@
         <v>139</v>
       </c>
       <c r="L68" t="s" s="2">
+        <v>407</v>
+      </c>
+      <c r="M68" t="s" s="2">
         <v>408</v>
-      </c>
-      <c r="M68" t="s" s="2">
-        <v>409</v>
       </c>
       <c r="N68" t="s" s="2">
         <v>253</v>
@@ -8706,7 +8701,7 @@
         <v>72</v>
       </c>
       <c r="AF68" t="s" s="2">
-        <v>407</v>
+        <v>406</v>
       </c>
       <c r="AG68" t="s" s="2">
         <v>73</v>
@@ -8723,14 +8718,14 @@
     </row>
     <row r="69" hidden="true">
       <c r="A69" t="s" s="2">
-        <v>410</v>
+        <v>409</v>
       </c>
       <c r="B69" t="s" s="2">
-        <v>410</v>
+        <v>409</v>
       </c>
       <c r="C69" s="2"/>
       <c r="D69" t="s" s="2">
-        <v>411</v>
+        <v>410</v>
       </c>
       <c r="E69" s="2"/>
       <c r="F69" t="s" s="2">
@@ -8749,16 +8744,16 @@
         <v>72</v>
       </c>
       <c r="K69" t="s" s="2">
+        <v>411</v>
+      </c>
+      <c r="L69" t="s" s="2">
         <v>412</v>
       </c>
-      <c r="L69" t="s" s="2">
+      <c r="M69" t="s" s="2">
         <v>413</v>
       </c>
-      <c r="M69" t="s" s="2">
-        <v>414</v>
-      </c>
       <c r="N69" t="s" s="2">
-        <v>368</v>
+        <v>367</v>
       </c>
       <c r="O69" s="2"/>
       <c r="P69" t="s" s="2">
@@ -8808,7 +8803,7 @@
         <v>72</v>
       </c>
       <c r="AF69" t="s" s="2">
-        <v>410</v>
+        <v>409</v>
       </c>
       <c r="AG69" t="s" s="2">
         <v>73</v>
@@ -8825,10 +8820,10 @@
     </row>
     <row r="70" hidden="true">
       <c r="A70" t="s" s="2">
-        <v>415</v>
+        <v>414</v>
       </c>
       <c r="B70" t="s" s="2">
-        <v>415</v>
+        <v>414</v>
       </c>
       <c r="C70" s="2"/>
       <c r="D70" t="s" s="2">
@@ -8851,13 +8846,13 @@
         <v>72</v>
       </c>
       <c r="K70" t="s" s="2">
+        <v>415</v>
+      </c>
+      <c r="L70" t="s" s="2">
         <v>416</v>
       </c>
-      <c r="L70" t="s" s="2">
+      <c r="M70" t="s" s="2">
         <v>417</v>
-      </c>
-      <c r="M70" t="s" s="2">
-        <v>418</v>
       </c>
       <c r="N70" s="2"/>
       <c r="O70" s="2"/>
@@ -8908,7 +8903,7 @@
         <v>72</v>
       </c>
       <c r="AF70" t="s" s="2">
-        <v>415</v>
+        <v>414</v>
       </c>
       <c r="AG70" t="s" s="2">
         <v>80</v>
@@ -8920,15 +8915,15 @@
         <v>92</v>
       </c>
       <c r="AJ70" t="s" s="2">
-        <v>419</v>
+        <v>418</v>
       </c>
     </row>
     <row r="71" hidden="true">
       <c r="A71" t="s" s="2">
-        <v>420</v>
+        <v>419</v>
       </c>
       <c r="B71" t="s" s="2">
-        <v>420</v>
+        <v>419</v>
       </c>
       <c r="C71" s="2"/>
       <c r="D71" t="s" s="2">
@@ -9025,10 +9020,10 @@
     </row>
     <row r="72" hidden="true">
       <c r="A72" t="s" s="2">
-        <v>421</v>
+        <v>420</v>
       </c>
       <c r="B72" t="s" s="2">
-        <v>421</v>
+        <v>420</v>
       </c>
       <c r="C72" s="2"/>
       <c r="D72" t="s" s="2">
@@ -9127,14 +9122,14 @@
     </row>
     <row r="73" hidden="true">
       <c r="A73" t="s" s="2">
-        <v>422</v>
+        <v>421</v>
       </c>
       <c r="B73" t="s" s="2">
-        <v>422</v>
+        <v>421</v>
       </c>
       <c r="C73" s="2"/>
       <c r="D73" t="s" s="2">
-        <v>423</v>
+        <v>422</v>
       </c>
       <c r="E73" s="2"/>
       <c r="F73" t="s" s="2">
@@ -9156,10 +9151,10 @@
         <v>124</v>
       </c>
       <c r="L73" t="s" s="2">
+        <v>423</v>
+      </c>
+      <c r="M73" t="s" s="2">
         <v>424</v>
-      </c>
-      <c r="M73" t="s" s="2">
-        <v>425</v>
       </c>
       <c r="N73" t="s" s="2">
         <v>171</v>
@@ -9214,7 +9209,7 @@
         <v>72</v>
       </c>
       <c r="AF73" t="s" s="2">
-        <v>426</v>
+        <v>425</v>
       </c>
       <c r="AG73" t="s" s="2">
         <v>73</v>
@@ -9231,10 +9226,10 @@
     </row>
     <row r="74" hidden="true">
       <c r="A74" t="s" s="2">
-        <v>427</v>
+        <v>426</v>
       </c>
       <c r="B74" t="s" s="2">
-        <v>427</v>
+        <v>426</v>
       </c>
       <c r="C74" s="2"/>
       <c r="D74" t="s" s="2">
@@ -9260,13 +9255,13 @@
         <v>211</v>
       </c>
       <c r="L74" t="s" s="2">
+        <v>427</v>
+      </c>
+      <c r="M74" t="s" s="2">
         <v>428</v>
       </c>
-      <c r="M74" t="s" s="2">
+      <c r="N74" t="s" s="2">
         <v>429</v>
-      </c>
-      <c r="N74" t="s" s="2">
-        <v>430</v>
       </c>
       <c r="O74" s="2"/>
       <c r="P74" t="s" s="2">
@@ -9295,11 +9290,11 @@
         <v>184</v>
       </c>
       <c r="Y74" t="s" s="2">
+        <v>430</v>
+      </c>
+      <c r="Z74" t="s" s="2">
         <v>431</v>
       </c>
-      <c r="Z74" t="s" s="2">
-        <v>432</v>
-      </c>
       <c r="AA74" t="s" s="2">
         <v>72</v>
       </c>
@@ -9316,7 +9311,7 @@
         <v>72</v>
       </c>
       <c r="AF74" t="s" s="2">
-        <v>427</v>
+        <v>426</v>
       </c>
       <c r="AG74" t="s" s="2">
         <v>73</v>
@@ -9333,10 +9328,10 @@
     </row>
     <row r="75" hidden="true">
       <c r="A75" t="s" s="2">
-        <v>433</v>
+        <v>432</v>
       </c>
       <c r="B75" t="s" s="2">
-        <v>433</v>
+        <v>432</v>
       </c>
       <c r="C75" s="2"/>
       <c r="D75" t="s" s="2">
@@ -9359,16 +9354,16 @@
         <v>81</v>
       </c>
       <c r="K75" t="s" s="2">
+        <v>433</v>
+      </c>
+      <c r="L75" t="s" s="2">
         <v>434</v>
       </c>
-      <c r="L75" t="s" s="2">
+      <c r="M75" t="s" s="2">
         <v>435</v>
       </c>
-      <c r="M75" t="s" s="2">
-        <v>436</v>
-      </c>
       <c r="N75" t="s" s="2">
-        <v>368</v>
+        <v>367</v>
       </c>
       <c r="O75" s="2"/>
       <c r="P75" t="s" s="2">
@@ -9418,7 +9413,7 @@
         <v>72</v>
       </c>
       <c r="AF75" t="s" s="2">
-        <v>433</v>
+        <v>432</v>
       </c>
       <c r="AG75" t="s" s="2">
         <v>73</v>
@@ -9435,10 +9430,10 @@
     </row>
     <row r="76" hidden="true">
       <c r="A76" t="s" s="2">
-        <v>437</v>
+        <v>436</v>
       </c>
       <c r="B76" t="s" s="2">
-        <v>437</v>
+        <v>436</v>
       </c>
       <c r="C76" s="2"/>
       <c r="D76" t="s" s="2">
@@ -9464,10 +9459,10 @@
         <v>101</v>
       </c>
       <c r="L76" t="s" s="2">
+        <v>437</v>
+      </c>
+      <c r="M76" t="s" s="2">
         <v>438</v>
-      </c>
-      <c r="M76" t="s" s="2">
-        <v>439</v>
       </c>
       <c r="N76" t="s" s="2">
         <v>253</v>
@@ -9499,11 +9494,11 @@
         <v>205</v>
       </c>
       <c r="Y76" t="s" s="2">
+        <v>439</v>
+      </c>
+      <c r="Z76" t="s" s="2">
         <v>440</v>
       </c>
-      <c r="Z76" t="s" s="2">
-        <v>441</v>
-      </c>
       <c r="AA76" t="s" s="2">
         <v>72</v>
       </c>
@@ -9520,7 +9515,7 @@
         <v>72</v>
       </c>
       <c r="AF76" t="s" s="2">
-        <v>437</v>
+        <v>436</v>
       </c>
       <c r="AG76" t="s" s="2">
         <v>73</v>
@@ -9537,10 +9532,10 @@
     </row>
     <row r="77" hidden="true">
       <c r="A77" t="s" s="2">
-        <v>442</v>
+        <v>441</v>
       </c>
       <c r="B77" t="s" s="2">
-        <v>442</v>
+        <v>441</v>
       </c>
       <c r="C77" s="2"/>
       <c r="D77" t="s" s="2">
@@ -9566,10 +9561,10 @@
         <v>101</v>
       </c>
       <c r="L77" t="s" s="2">
+        <v>442</v>
+      </c>
+      <c r="M77" t="s" s="2">
         <v>443</v>
-      </c>
-      <c r="M77" t="s" s="2">
-        <v>444</v>
       </c>
       <c r="N77" t="s" s="2">
         <v>253</v>
@@ -9602,7 +9597,7 @@
       </c>
       <c r="Y77" s="2"/>
       <c r="Z77" t="s" s="2">
-        <v>445</v>
+        <v>444</v>
       </c>
       <c r="AA77" t="s" s="2">
         <v>72</v>
@@ -9620,7 +9615,7 @@
         <v>72</v>
       </c>
       <c r="AF77" t="s" s="2">
-        <v>442</v>
+        <v>441</v>
       </c>
       <c r="AG77" t="s" s="2">
         <v>80</v>
@@ -9637,10 +9632,10 @@
     </row>
     <row r="78" hidden="true">
       <c r="A78" t="s" s="2">
-        <v>446</v>
+        <v>445</v>
       </c>
       <c r="B78" t="s" s="2">
-        <v>446</v>
+        <v>445</v>
       </c>
       <c r="C78" s="2"/>
       <c r="D78" t="s" s="2">
@@ -9666,10 +9661,10 @@
         <v>294</v>
       </c>
       <c r="L78" t="s" s="2">
+        <v>446</v>
+      </c>
+      <c r="M78" t="s" s="2">
         <v>447</v>
-      </c>
-      <c r="M78" t="s" s="2">
-        <v>448</v>
       </c>
       <c r="N78" t="s" s="2">
         <v>297</v>
@@ -9722,7 +9717,7 @@
         <v>72</v>
       </c>
       <c r="AF78" t="s" s="2">
-        <v>446</v>
+        <v>445</v>
       </c>
       <c r="AG78" t="s" s="2">
         <v>73</v>
@@ -9739,10 +9734,10 @@
     </row>
     <row r="79" hidden="true">
       <c r="A79" t="s" s="2">
-        <v>449</v>
+        <v>448</v>
       </c>
       <c r="B79" t="s" s="2">
-        <v>449</v>
+        <v>448</v>
       </c>
       <c r="C79" s="2"/>
       <c r="D79" t="s" s="2">
@@ -9768,13 +9763,13 @@
         <v>294</v>
       </c>
       <c r="L79" t="s" s="2">
+        <v>449</v>
+      </c>
+      <c r="M79" t="s" s="2">
         <v>450</v>
       </c>
-      <c r="M79" t="s" s="2">
+      <c r="N79" t="s" s="2">
         <v>451</v>
-      </c>
-      <c r="N79" t="s" s="2">
-        <v>452</v>
       </c>
       <c r="O79" s="2"/>
       <c r="P79" t="s" s="2">
@@ -9824,7 +9819,7 @@
         <v>72</v>
       </c>
       <c r="AF79" t="s" s="2">
-        <v>449</v>
+        <v>448</v>
       </c>
       <c r="AG79" t="s" s="2">
         <v>73</v>

--- a/main/ig/StructureDefinition-sas-sos-appointment.xlsx
+++ b/main/ig/StructureDefinition-sas-sos-appointment.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-18T14:54:32+00:00</t>
+    <t>2026-08-19T07:30:40+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-sas-sos-appointment.xlsx
+++ b/main/ig/StructureDefinition-sas-sos-appointment.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-19T07:30:40+00:00</t>
+    <t>2026-08-19T11:37:26+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-sas-sos-appointment.xlsx
+++ b/main/ig/StructureDefinition-sas-sos-appointment.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-19T11:37:26+00:00</t>
+    <t>2026-08-19T11:59:01+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-sas-sos-appointment.xlsx
+++ b/main/ig/StructureDefinition-sas-sos-appointment.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-19T11:59:01+00:00</t>
+    <t>2026-08-20T07:20:42+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-sas-sos-appointment.xlsx
+++ b/main/ig/StructureDefinition-sas-sos-appointment.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-20T07:20:42+00:00</t>
+    <t>2026-09-08T08:23:10+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-sas-sos-appointment.xlsx
+++ b/main/ig/StructureDefinition-sas-sos-appointment.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-08T08:23:10+00:00</t>
+    <t>2026-09-10T10:05:58+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-sas-sos-appointment.xlsx
+++ b/main/ig/StructureDefinition-sas-sos-appointment.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-10T10:05:58+00:00</t>
+    <t>2026-09-11T14:02:19+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
